--- a/engagement_survey_forms/002_team_communication_effectiveness_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/002_team_communication_effectiveness_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Almost Always'}</t>
+          <t>Almost Always</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'chat'}</t>
+          <t>chat</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Chat'}</t>
+          <t>Chat</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'text_message'}</t>
+          <t>text_message</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Text message'}</t>
+          <t>Text message</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Video call'}</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'video_call'}</t>
+          <t>video_call</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Video call'}</t>
+          <t>Video call</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'shared_doc'}</t>
+          <t>shared_doc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Shared doc'}</t>
+          <t>Shared doc</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'task_list'}</t>
+          <t>task_list</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Task list'}</t>
+          <t>Task list</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'avoid'}</t>
+          <t>avoid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Avoid'}</t>
+          <t>Avoid</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Address'}</t>
+          <t>Address</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'delegate'}</t>
+          <t>delegate</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Delegate'}</t>
+          <t>Delegate</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'refer_to_a_third_party'}</t>
+          <t>refer_to_a_third_party</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Refer to a third party'}</t>
+          <t>Refer to a third party</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'save_and_continue_later'}</t>
+          <t>save_and_continue_later</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Save and Continue Later'}</t>
+          <t>Save and Continue Later</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'in_person'}</t>
+          <t>in_person</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'In person'}</t>
+          <t>In person</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'computer'}</t>
+          <t>computer</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Computer'}</t>
+          <t>Computer</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'confirm'}</t>
+          <t>confirm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Confirm'}</t>
+          <t>Confirm</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'no_confirm'}</t>
+          <t>no_confirm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'No confirm'}</t>
+          <t>No confirm</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'agree'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Agree'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'disagree'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
